--- a/0-DocumentationEducationCompetense/Business-theme.xlsx
+++ b/0-DocumentationEducationCompetense/Business-theme.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73fe6e1701840021/Documents/_Omistukset/General model of value addition/0-DocumentationEducationCompetense/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73fe6e1701840021/Documents/_Omistukset/Generic model of value addition/0-DocumentationEducationCompetense/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="34" documentId="8_{83434DCC-FF0A-4F8F-B4D3-7E7022F8FBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D496617-5461-4323-B18E-31A926A5847F}"/>
@@ -1493,12 +1493,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="90"/>
     </xf>
@@ -1583,6 +1577,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="90"/>
     </xf>
@@ -1594,6 +1591,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2818,6 +2818,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3254,10 +3258,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -3270,25 +3274,25 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="24" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="44"/>
@@ -3300,36 +3304,36 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="52" t="s">
         <v>14</v>
       </c>
@@ -3339,24 +3343,24 @@
       <c r="I11" s="61"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="25" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="106" t="s">
         <v>11</v>
       </c>
@@ -3394,10 +3398,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="88" t="s">
@@ -3410,25 +3414,25 @@
       <c r="I4" s="108"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="24" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="44"/>
@@ -3440,36 +3444,36 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="59" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="59" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="59" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="60" t="s">
         <v>14</v>
       </c>
@@ -3479,8 +3483,8 @@
       <c r="I11" s="61"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="25" t="s">
         <v>13</v>
       </c>
@@ -3491,8 +3495,8 @@
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
@@ -3500,8 +3504,8 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="106" t="s">
         <v>11</v>
       </c>
@@ -3539,10 +3543,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -3555,8 +3559,8 @@
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="57" t="s">
         <v>8</v>
       </c>
@@ -3567,17 +3571,17 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
@@ -3589,44 +3593,44 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="41" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="54" t="s">
         <v>13</v>
       </c>
@@ -3637,8 +3641,8 @@
       <c r="I12" s="23"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="54" t="s">
         <v>12</v>
       </c>
@@ -3646,8 +3650,8 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="110" t="s">
         <v>11</v>
       </c>
@@ -3685,10 +3689,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="111" t="s">
@@ -3701,8 +3705,8 @@
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="64" t="s">
         <v>8</v>
       </c>
@@ -3713,8 +3717,8 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="65" t="s">
         <v>23</v>
       </c>
@@ -3725,9 +3729,9 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
@@ -3739,44 +3743,44 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="41" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="64" t="s">
         <v>13</v>
       </c>
@@ -3787,8 +3791,8 @@
       <c r="I12" s="23"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="64" t="s">
         <v>12</v>
       </c>
@@ -3796,8 +3800,8 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="112" t="s">
         <v>11</v>
       </c>
@@ -3835,10 +3839,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -3851,8 +3855,8 @@
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
@@ -3863,8 +3867,8 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
@@ -3875,9 +3879,9 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
@@ -3889,36 +3893,36 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="28" t="s">
         <v>14</v>
       </c>
@@ -3928,8 +3932,8 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="57" t="s">
         <v>13</v>
       </c>
@@ -3940,16 +3944,16 @@
       <c r="I12" s="23"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="106" t="s">
         <v>11</v>
       </c>
@@ -3987,10 +3991,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -4003,8 +4007,8 @@
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
@@ -4015,8 +4019,8 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
@@ -4027,9 +4031,9 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
@@ -4041,36 +4045,36 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="28" t="s">
         <v>14</v>
       </c>
@@ -4080,8 +4084,8 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
@@ -4092,8 +4096,8 @@
       <c r="I12" s="23"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="57" t="s">
         <v>12</v>
       </c>
@@ -4104,8 +4108,8 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="106" t="s">
         <v>11</v>
       </c>
@@ -4143,10 +4147,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -4159,8 +4163,8 @@
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
@@ -4171,8 +4175,8 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
@@ -4183,9 +4187,9 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
@@ -4197,36 +4201,36 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="28" t="s">
         <v>14</v>
       </c>
@@ -4236,8 +4240,8 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
@@ -4248,8 +4252,8 @@
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
@@ -4260,8 +4264,8 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="113" t="s">
         <v>11</v>
       </c>
@@ -4318,10 +4322,10 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="155" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="22" t="s">
@@ -4333,8 +4337,8 @@
       <c r="H4" s="72"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="141"/>
-      <c r="C5" s="141"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
       <c r="D5" s="22" t="s">
         <v>8</v>
       </c>
@@ -4351,8 +4355,8 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="141"/>
-      <c r="C6" s="141"/>
+      <c r="B6" s="139"/>
+      <c r="C6" s="139"/>
       <c r="D6" s="91" t="s">
         <v>23</v>
       </c>
@@ -4371,8 +4375,8 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
       <c r="D7" s="93" t="s">
         <v>18</v>
       </c>
@@ -4384,8 +4388,8 @@
       <c r="H7" s="94"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="141"/>
-      <c r="C8" s="141"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
       <c r="D8" s="46" t="s">
         <v>17</v>
       </c>
@@ -4404,8 +4408,8 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="141"/>
-      <c r="C9" s="141"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
       <c r="D9" s="46" t="s">
         <v>22</v>
       </c>
@@ -4422,8 +4426,8 @@
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="141"/>
-      <c r="C10" s="141"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
       <c r="D10" s="46" t="s">
         <v>16</v>
       </c>
@@ -4440,8 +4444,8 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
       <c r="D11" s="85" t="s">
         <v>14</v>
       </c>
@@ -4458,8 +4462,8 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="141"/>
-      <c r="C12" s="141"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="139"/>
       <c r="D12" s="88" t="s">
         <v>13</v>
       </c>
@@ -4476,8 +4480,8 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="141"/>
-      <c r="C13" s="141"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="139"/>
       <c r="D13" s="30" t="s">
         <v>12</v>
       </c>
@@ -4487,8 +4491,8 @@
       <c r="H13" s="84"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
       <c r="D14" s="22" t="s">
         <v>11</v>
       </c>
@@ -4553,10 +4557,10 @@
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="155" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="22" t="s">
@@ -4568,8 +4572,8 @@
       <c r="H4" s="72"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="141"/>
-      <c r="C5" s="141"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
       <c r="D5" s="22" t="s">
         <v>8</v>
       </c>
@@ -4586,8 +4590,8 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="141"/>
-      <c r="C6" s="141"/>
+      <c r="B6" s="139"/>
+      <c r="C6" s="139"/>
       <c r="D6" s="39" t="s">
         <v>23</v>
       </c>
@@ -4606,8 +4610,8 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
       <c r="D7" s="45" t="s">
         <v>18</v>
       </c>
@@ -4619,8 +4623,8 @@
       <c r="H7" s="94"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="141"/>
-      <c r="C8" s="141"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
       <c r="D8" s="46" t="s">
         <v>17</v>
       </c>
@@ -4639,8 +4643,8 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="141"/>
-      <c r="C9" s="141"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
       <c r="D9" s="48" t="s">
         <v>22</v>
       </c>
@@ -4657,8 +4661,8 @@
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="141"/>
-      <c r="C10" s="141"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
       <c r="D10" s="46" t="s">
         <v>16</v>
       </c>
@@ -4675,8 +4679,8 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
       <c r="D11" s="47" t="s">
         <v>14</v>
       </c>
@@ -4693,8 +4697,8 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="141"/>
-      <c r="C12" s="141"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="139"/>
       <c r="D12" s="43" t="s">
         <v>13</v>
       </c>
@@ -4711,8 +4715,8 @@
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="141"/>
-      <c r="C13" s="141"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="139"/>
       <c r="D13" s="56" t="s">
         <v>12</v>
       </c>
@@ -4729,8 +4733,8 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
       <c r="D14" s="22" t="s">
         <v>11</v>
       </c>
@@ -4796,10 +4800,10 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="155" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="56" t="s">
@@ -4820,8 +4824,8 @@
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="141"/>
-      <c r="C5" s="141"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
       <c r="D5" s="22" t="s">
         <v>8</v>
       </c>
@@ -4838,8 +4842,8 @@
       </c>
     </row>
     <row r="6" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="141"/>
-      <c r="C6" s="141"/>
+      <c r="B6" s="139"/>
+      <c r="C6" s="139"/>
       <c r="D6" s="39" t="s">
         <v>23</v>
       </c>
@@ -4858,8 +4862,8 @@
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
       <c r="D7" s="45" t="s">
         <v>18</v>
       </c>
@@ -4871,8 +4875,8 @@
       <c r="H7" s="98"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="141"/>
-      <c r="C8" s="141"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
       <c r="D8" s="46" t="s">
         <v>17</v>
       </c>
@@ -4891,8 +4895,8 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="141"/>
-      <c r="C9" s="141"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
       <c r="D9" s="46" t="s">
         <v>22</v>
       </c>
@@ -4909,8 +4913,8 @@
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="141"/>
-      <c r="C10" s="141"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
       <c r="D10" s="46" t="s">
         <v>16</v>
       </c>
@@ -4927,8 +4931,8 @@
       </c>
     </row>
     <row r="11" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
       <c r="D11" s="47" t="s">
         <v>14</v>
       </c>
@@ -4945,8 +4949,8 @@
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="141"/>
-      <c r="C12" s="141"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="139"/>
       <c r="D12" s="30" t="s">
         <v>13</v>
       </c>
@@ -4963,8 +4967,8 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="141"/>
-      <c r="C13" s="141"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="139"/>
       <c r="D13" s="22" t="s">
         <v>12</v>
       </c>
@@ -4982,8 +4986,8 @@
       <c r="K13" s="26"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
       <c r="D14" s="56" t="s">
         <v>11</v>
       </c>
@@ -5032,7 +5036,7 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="126" t="s">
+      <c r="B4" s="124" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="6"/>
@@ -5044,53 +5048,53 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="127"/>
+      <c r="B5" s="125"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="127"/>
+      <c r="B6" s="125"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="127"/>
+      <c r="B7" s="125"/>
       <c r="C7" s="123"/>
       <c r="D7" s="123"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="127"/>
+      <c r="B8" s="125"/>
       <c r="C8" s="123"/>
       <c r="D8" s="123"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="127"/>
+      <c r="B9" s="125"/>
       <c r="C9" s="123"/>
       <c r="D9" s="123"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="127"/>
+      <c r="B10" s="125"/>
       <c r="C10" s="123"/>
       <c r="D10" s="123"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="127"/>
+      <c r="B11" s="125"/>
       <c r="C11" s="123"/>
       <c r="D11" s="123"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="127"/>
+      <c r="B12" s="125"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="127"/>
+      <c r="B13" s="125"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="128"/>
+      <c r="B14" s="126"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -5135,10 +5139,10 @@
       </c>
     </row>
     <row r="4" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="152" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="152" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="21" t="s">
@@ -5154,8 +5158,8 @@
       </c>
     </row>
     <row r="5" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
@@ -5168,8 +5172,8 @@
       </c>
     </row>
     <row r="6" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="124"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="152"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
@@ -5182,9 +5186,9 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="124"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="125" t="s">
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="157" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
@@ -5199,9 +5203,9 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="125"/>
+      <c r="B8" s="152"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="157"/>
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
@@ -5210,9 +5214,9 @@
       </c>
     </row>
     <row r="9" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="124"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="125"/>
+      <c r="B9" s="152"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="157"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
@@ -5221,9 +5225,9 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="125"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="157"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
@@ -5232,9 +5236,9 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="125"/>
+      <c r="B11" s="152"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="157"/>
       <c r="E11" s="28" t="s">
         <v>14</v>
       </c>
@@ -5247,8 +5251,8 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="152"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
@@ -5261,8 +5265,8 @@
       </c>
     </row>
     <row r="13" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="152"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
@@ -5275,8 +5279,8 @@
       </c>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="152"/>
       <c r="D14" s="21" t="s">
         <v>11</v>
       </c>
@@ -5312,10 +5316,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="130" t="s">
+      <c r="B4" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="C4" s="124" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="6"/>
@@ -5326,63 +5330,63 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="131"/>
-      <c r="C5" s="127"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="125"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="131"/>
-      <c r="C6" s="127"/>
+      <c r="B6" s="129"/>
+      <c r="C6" s="125"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="131"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="129"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="127"/>
       <c r="E7" s="123"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="131"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="129"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="127"/>
       <c r="E8" s="123"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="131"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="129"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="127"/>
       <c r="E9" s="123"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="131"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="129"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="127"/>
       <c r="E10" s="123"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="131"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="127"/>
       <c r="E11" s="123"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="131"/>
-      <c r="C12" s="127"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="125"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="131"/>
-      <c r="C13" s="127"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="125"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="132"/>
-      <c r="C14" s="128"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="126"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -5415,10 +5419,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="130" t="s">
+      <c r="B4" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="133" t="s">
+      <c r="C4" s="131" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="49" t="s">
@@ -5431,80 +5435,80 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="131"/>
-      <c r="C5" s="134"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="132"/>
       <c r="D5" s="50" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="131"/>
-      <c r="C6" s="134"/>
+      <c r="B6" s="129"/>
+      <c r="C6" s="132"/>
       <c r="D6" s="50" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="131"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="129"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="127"/>
       <c r="F7" s="123"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="131"/>
-      <c r="C8" s="134"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="129"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="127"/>
       <c r="F8" s="123"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="131"/>
-      <c r="C9" s="134"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="129"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="127"/>
       <c r="F9" s="123"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="131"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="129"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="127"/>
       <c r="F10" s="123"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="131"/>
-      <c r="C11" s="134"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="127"/>
       <c r="F11" s="123"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="131"/>
-      <c r="C12" s="134"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="132"/>
       <c r="D12" s="50" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="131"/>
-      <c r="C13" s="134"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="132"/>
       <c r="D13" s="50" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="132"/>
-      <c r="C14" s="135"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="133"/>
       <c r="D14" s="51" t="s">
         <v>11</v>
       </c>
@@ -5546,10 +5550,10 @@
   <sheetData>
     <row r="3" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="137" t="s">
+      <c r="B4" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="C4" s="138" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -5562,25 +5566,25 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="138"/>
-      <c r="C5" s="141"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="139"/>
       <c r="D5" s="25" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="138"/>
-      <c r="C6" s="141"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="139"/>
       <c r="D6" s="24" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="138"/>
-      <c r="C7" s="142"/>
-      <c r="D7" s="144" t="s">
+      <c r="B7" s="136"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="142" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
@@ -5591,33 +5595,33 @@
       <c r="J7" s="123"/>
     </row>
     <row r="8" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="138"/>
-      <c r="C8" s="142"/>
-      <c r="D8" s="145"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="143"/>
       <c r="H8" s="31"/>
       <c r="I8" s="1"/>
       <c r="J8" s="123"/>
     </row>
     <row r="9" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="138"/>
-      <c r="C9" s="142"/>
-      <c r="D9" s="145"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="143"/>
       <c r="G9" s="31"/>
       <c r="I9" s="1"/>
       <c r="J9" s="123"/>
     </row>
     <row r="10" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="138"/>
-      <c r="C10" s="142"/>
-      <c r="D10" s="145"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="143"/>
       <c r="F10" s="31"/>
       <c r="I10" s="1"/>
       <c r="J10" s="123"/>
     </row>
     <row r="11" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="138"/>
-      <c r="C11" s="142"/>
-      <c r="D11" s="146"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="144"/>
       <c r="E11" s="36"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -5626,24 +5630,24 @@
       <c r="J11" s="123"/>
     </row>
     <row r="12" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="138"/>
-      <c r="C12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="139"/>
       <c r="D12" s="25" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="138"/>
-      <c r="C13" s="141"/>
+      <c r="B13" s="136"/>
+      <c r="C13" s="139"/>
       <c r="D13" s="25" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="139"/>
-      <c r="C14" s="143"/>
+      <c r="B14" s="137"/>
+      <c r="C14" s="141"/>
       <c r="D14" s="103" t="s">
         <v>11</v>
       </c>
@@ -5684,10 +5688,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="137" t="s">
+      <c r="B4" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="C4" s="138" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="104" t="s">
@@ -5700,25 +5704,25 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="138"/>
-      <c r="C5" s="141"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="139"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="138"/>
-      <c r="C6" s="141"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="139"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="138"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="147" t="s">
+      <c r="B7" s="136"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="145" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="44"/>
@@ -5728,30 +5732,30 @@
       <c r="I7" s="105"/>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="138"/>
-      <c r="C8" s="141"/>
-      <c r="D8" s="148"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="146"/>
       <c r="H8" s="31"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="138"/>
-      <c r="C9" s="141"/>
-      <c r="D9" s="148"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="146"/>
       <c r="G9" s="31"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="138"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="148"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="146"/>
       <c r="F10" s="31"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="138"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="149"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="147"/>
       <c r="E11" s="53" t="s">
         <v>14</v>
       </c>
@@ -5761,24 +5765,24 @@
       <c r="I11" s="61"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="138"/>
-      <c r="C12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="139"/>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="138"/>
-      <c r="C13" s="141"/>
+      <c r="B13" s="136"/>
+      <c r="C13" s="139"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="139"/>
-      <c r="C14" s="143"/>
+      <c r="B14" s="137"/>
+      <c r="C14" s="141"/>
       <c r="D14" s="103" t="s">
         <v>11</v>
       </c>
@@ -5816,10 +5820,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -5832,25 +5836,25 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="44"/>
@@ -5860,32 +5864,32 @@
       <c r="I7" s="105"/>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="31"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="31"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="37" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="52" t="s">
         <v>14</v>
       </c>
@@ -5895,24 +5899,24 @@
       <c r="I11" s="61"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="106" t="s">
         <v>11</v>
       </c>
@@ -5951,10 +5955,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -5967,25 +5971,25 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="44"/>
@@ -5995,34 +5999,34 @@
       <c r="I7" s="105"/>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="31"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="52" t="s">
         <v>14</v>
       </c>
@@ -6032,24 +6036,24 @@
       <c r="I11" s="61"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="106" t="s">
         <v>11</v>
       </c>
@@ -6087,10 +6091,10 @@
   <sheetData>
     <row r="3" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="102" t="s">
@@ -6103,25 +6107,25 @@
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="151"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="151"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="151"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="149"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="154" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="44"/>
@@ -6131,36 +6135,36 @@
       <c r="I7" s="105"/>
     </row>
     <row r="8" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="155"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="154"/>
       <c r="H8" s="37" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="155"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="154"/>
       <c r="G9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="155"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="154"/>
       <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="151"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="155"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="55" t="s">
         <v>14</v>
       </c>
@@ -6170,24 +6174,24 @@
       <c r="I11" s="61"/>
     </row>
     <row r="12" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="151"/>
-      <c r="C12" s="124"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="21" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="151"/>
-      <c r="C13" s="124"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="152"/>
       <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="152"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="106" t="s">
         <v>11</v>
       </c>
